--- a/Day6.xlsx
+++ b/Day6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1876289E-4ECB-DD42-B597-726C1BD6C8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED13F14-F163-0046-BDD2-86515C01FE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28420" windowHeight="17400" activeTab="3" xr2:uid="{153C5096-2AF6-744A-A6D3-34BD6510552E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28420" windowHeight="17400" activeTab="3" xr2:uid="{153C5096-2AF6-744A-A6D3-34BD6510552E}"/>
   </bookViews>
   <sheets>
     <sheet name="agenda" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="115">
   <si>
     <t>RANK</t>
   </si>
@@ -373,6 +373,39 @@
   </si>
   <si>
     <t>Find some value in a array based on sum conditions ( LOOKUP )</t>
+  </si>
+  <si>
+    <t>To find index of a given value</t>
+  </si>
+  <si>
+    <t>5th pos</t>
+  </si>
+  <si>
+    <t>LESS THAN ( 1 ) array must be in Ascending ordering</t>
+  </si>
+  <si>
+    <t>2nd pos</t>
+  </si>
+  <si>
+    <t>GREATER THAN (-1) array must be in Descending order</t>
+  </si>
+  <si>
+    <t>0-18</t>
+  </si>
+  <si>
+    <t>19-35</t>
+  </si>
+  <si>
+    <t>36-60</t>
+  </si>
+  <si>
+    <t>60+</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>upp</t>
   </si>
 </sst>
 </file>
@@ -506,8 +539,8 @@
       <xdr:row>5</xdr:row>
       <xdr:rowOff>37063</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="17" name="Ink 16">
@@ -526,7 +559,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="17" name="Ink 16">
@@ -571,8 +604,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>198484</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="27" name="Ink 26">
@@ -591,7 +624,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="27" name="Ink 26">
@@ -641,8 +674,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>200455</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="15" name="Ink 14">
@@ -661,7 +694,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="15" name="Ink 14">
@@ -750,8 +783,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>118898</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="17" name="Ink 16">
@@ -770,7 +803,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="17" name="Ink 16">
@@ -815,8 +848,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>41801</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="18" name="Ink 17">
@@ -835,7 +868,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="18" name="Ink 17">
@@ -880,8 +913,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>128283</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="19" name="Ink 18">
@@ -900,7 +933,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="19" name="Ink 18">
@@ -945,8 +978,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>106487</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="20" name="Ink 19">
@@ -965,7 +998,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="20" name="Ink 19">
@@ -1054,8 +1087,8 @@
       <xdr:row>89</xdr:row>
       <xdr:rowOff>582</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="25" name="Ink 24">
@@ -1074,7 +1107,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="25" name="Ink 24">
@@ -1678,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1126B9DF-1B8E-F845-B8E3-FA7F502314C2}">
-  <dimension ref="A4:I35"/>
+  <dimension ref="A4:I76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
@@ -1771,6 +1804,161 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B52" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B54" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E54" s="6"/>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B56" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="6"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B58" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="5"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B65" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B67" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>102</v>
+      </c>
+      <c r="D69" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B76" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2676,7 +2864,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{351F083F-D949-A649-BA74-4FC8A0419922}">
-  <dimension ref="B4:L53"/>
+  <dimension ref="B4:L49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="2:12" x14ac:dyDescent="0.2">
@@ -2813,7 +3001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
         <v>67</v>
       </c>
@@ -2824,154 +3012,176 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B36" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B40" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B42" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="5"/>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B49" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B51" s="9" t="s">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
         <v>100</v>
       </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" t="s">
-        <v>103</v>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <f>MATCH("Arjun",B12:E12,0)</f>
+        <v>2</v>
+      </c>
+      <c r="G31">
+        <v>5</v>
+      </c>
+      <c r="I31">
+        <f>MATCH(7,G28:G34,1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="G32" s="1">
+        <v>6</v>
+      </c>
+      <c r="H32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F37" s="1">
+        <v>8</v>
+      </c>
+      <c r="G37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="H38">
+        <f>MATCH(7,F36:F43,-1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="44" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="K44">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>113</v>
+      </c>
+      <c r="I45" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="G46" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="G47" t="s">
+        <v>110</v>
+      </c>
+      <c r="H47">
+        <v>19</v>
+      </c>
+      <c r="I47">
+        <v>35</v>
+      </c>
+      <c r="K47">
+        <f>MATCH(K44,H46:H49,1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="G48" t="s">
+        <v>111</v>
+      </c>
+      <c r="H48">
+        <v>36</v>
+      </c>
+      <c r="I48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G49" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
